--- a/2022 data/excel_outputs/154_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/154_boothwise_data.xlsx
@@ -14,11 +14,92 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="537">
   <si>
     <t>AC 154 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
+    <t>Unnamed: 27</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -499,7 +580,7 @@
     <t>P.P. RAMPURA KHAMARIYA R.N.1</t>
   </si>
   <si>
-    <t>P.P. RAMPURA KHAMARIYA R.N.■</t>
+    <t>RA0I0KU0U0MA0$V0 SAVAYAJAPARU K0N0 1</t>
   </si>
   <si>
     <t>P.P. KANHARI</t>
@@ -1006,7 +1087,7 @@
     <t>P.P. BARRA R.N.1</t>
   </si>
   <si>
-    <t>P.P. BARRA R.N.■</t>
+    <t>A0PA0 LAMAKAN K0N0 1</t>
   </si>
   <si>
     <t>P.P. BAMHTAPUR NANDBAG</t>
@@ -1550,8 +1631,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1567,7 +1656,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1575,12 +1664,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1879,94 +1986,175 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:28">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>484</v>
+        <v>511</v>
       </c>
       <c r="D2" t="s">
-        <v>485</v>
+        <v>512</v>
       </c>
       <c r="E2" t="s">
-        <v>486</v>
+        <v>513</v>
       </c>
       <c r="F2" t="s">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="G2" t="s">
-        <v>488</v>
+        <v>515</v>
       </c>
       <c r="H2" t="s">
-        <v>489</v>
+        <v>516</v>
       </c>
       <c r="I2" t="s">
-        <v>490</v>
+        <v>517</v>
       </c>
       <c r="J2" t="s">
-        <v>491</v>
+        <v>518</v>
       </c>
       <c r="K2" t="s">
-        <v>492</v>
+        <v>519</v>
       </c>
       <c r="L2" t="s">
-        <v>493</v>
+        <v>520</v>
       </c>
       <c r="M2" t="s">
-        <v>494</v>
+        <v>521</v>
       </c>
       <c r="N2" t="s">
-        <v>495</v>
+        <v>522</v>
       </c>
       <c r="O2" t="s">
-        <v>496</v>
+        <v>523</v>
       </c>
       <c r="P2" t="s">
-        <v>497</v>
+        <v>524</v>
       </c>
       <c r="Q2" t="s">
-        <v>498</v>
+        <v>525</v>
       </c>
       <c r="R2" t="s">
-        <v>499</v>
+        <v>526</v>
       </c>
       <c r="S2" t="s">
-        <v>500</v>
+        <v>527</v>
       </c>
       <c r="T2" t="s">
-        <v>501</v>
+        <v>528</v>
       </c>
       <c r="U2" t="s">
-        <v>502</v>
+        <v>529</v>
       </c>
       <c r="V2" t="s">
-        <v>503</v>
+        <v>530</v>
       </c>
       <c r="W2" t="s">
-        <v>504</v>
+        <v>531</v>
       </c>
       <c r="X2" t="s">
-        <v>505</v>
+        <v>532</v>
       </c>
       <c r="Y2" t="s">
-        <v>506</v>
+        <v>533</v>
       </c>
       <c r="Z2" t="s">
-        <v>507</v>
+        <v>534</v>
       </c>
       <c r="AA2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="AB2" t="s">
-        <v>509</v>
+        <v>536</v>
       </c>
     </row>
     <row r="3" spans="1:28">
@@ -1974,7 +2162,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C3">
         <v>1050</v>
@@ -2060,7 +2248,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>696</v>
@@ -2146,7 +2334,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>983</v>
@@ -2232,7 +2420,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>543</v>
@@ -2318,7 +2506,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>874</v>
@@ -2404,7 +2592,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>849</v>
@@ -2490,7 +2678,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>849</v>
@@ -2576,7 +2764,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="C10">
         <v>859</v>
@@ -2662,7 +2850,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C11">
         <v>858</v>
@@ -2748,7 +2936,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C12">
         <v>866</v>
@@ -2834,7 +3022,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C13">
         <v>683</v>
@@ -2920,7 +3108,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C14">
         <v>767</v>
@@ -3006,7 +3194,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C15">
         <v>782</v>
@@ -3092,7 +3280,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C16">
         <v>654</v>
@@ -3178,7 +3366,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="C17">
         <v>1061</v>
@@ -3264,7 +3452,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="C18">
         <v>697</v>
@@ -3350,7 +3538,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="C19">
         <v>854</v>
@@ -3436,7 +3624,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="C20">
         <v>918</v>
@@ -3522,7 +3710,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="C21">
         <v>952</v>
@@ -3608,7 +3796,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="C22">
         <v>561</v>
@@ -3694,7 +3882,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C23">
         <v>1067</v>
@@ -3780,7 +3968,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="C24">
         <v>820</v>
@@ -3866,7 +4054,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="C25">
         <v>432</v>
@@ -3952,7 +4140,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C26">
         <v>1007</v>
@@ -4038,7 +4226,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="C27">
         <v>975</v>
@@ -4124,7 +4312,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="C28">
         <v>688</v>
@@ -4210,7 +4398,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="C29">
         <v>446</v>
@@ -4296,7 +4484,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="C30">
         <v>585</v>
@@ -4382,7 +4570,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C31">
         <v>749</v>
@@ -4468,7 +4656,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="C32">
         <v>924</v>
@@ -4554,7 +4742,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C33">
         <v>675</v>
@@ -4640,7 +4828,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C34">
         <v>666</v>
@@ -4726,7 +4914,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="C35">
         <v>1124</v>
@@ -4812,7 +5000,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="C36">
         <v>763</v>
@@ -4898,7 +5086,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="C37">
         <v>693</v>
@@ -4984,7 +5172,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C38">
         <v>791</v>
@@ -5070,7 +5258,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C39">
         <v>1080</v>
@@ -5156,7 +5344,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="C40">
         <v>513</v>
@@ -5242,7 +5430,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C41">
         <v>1028</v>
@@ -5328,7 +5516,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="C42">
         <v>955</v>
@@ -5414,7 +5602,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C43">
         <v>1209</v>
@@ -5500,7 +5688,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C44">
         <v>782</v>
@@ -5586,7 +5774,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="C45">
         <v>1059</v>
@@ -5672,7 +5860,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="C46">
         <v>893</v>
@@ -5758,7 +5946,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C47">
         <v>698</v>
@@ -5844,7 +6032,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="C48">
         <v>851</v>
@@ -5930,7 +6118,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="C49">
         <v>682</v>
@@ -6016,7 +6204,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C50">
         <v>792</v>
@@ -6102,7 +6290,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="C51">
         <v>690</v>
@@ -6188,7 +6376,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="C52">
         <v>593</v>
@@ -6274,7 +6462,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="C53">
         <v>787</v>
@@ -6360,7 +6548,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="C54">
         <v>946</v>
@@ -6446,7 +6634,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C55">
         <v>439</v>
@@ -6532,7 +6720,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="C56">
         <v>1036</v>
@@ -6618,7 +6806,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="C57">
         <v>1179</v>
@@ -6704,7 +6892,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="C58">
         <v>676</v>
@@ -6790,7 +6978,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="C59">
         <v>645</v>
@@ -6876,7 +7064,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="C60">
         <v>861</v>
@@ -6962,7 +7150,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="C61">
         <v>1114</v>
@@ -7048,7 +7236,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="C62">
         <v>1190</v>
@@ -7134,7 +7322,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="C63">
         <v>795</v>
@@ -7220,7 +7408,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="C64">
         <v>333</v>
@@ -7306,7 +7494,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="C65">
         <v>596</v>
@@ -7392,7 +7580,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="C66">
         <v>666</v>
@@ -7478,7 +7666,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="C67">
         <v>898</v>
@@ -7564,7 +7752,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="C68">
         <v>726</v>
@@ -7650,7 +7838,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="C69">
         <v>833</v>
@@ -7736,7 +7924,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C70">
         <v>789</v>
@@ -7822,7 +8010,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="C71">
         <v>615</v>
@@ -7908,7 +8096,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="C72">
         <v>1007</v>
@@ -7994,7 +8182,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="C73">
         <v>801</v>
@@ -8080,7 +8268,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="C74">
         <v>567</v>
@@ -8166,7 +8354,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="C75">
         <v>1017</v>
@@ -8252,7 +8440,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="C76">
         <v>1152</v>
@@ -8338,7 +8526,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="C77">
         <v>720</v>
@@ -8424,7 +8612,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="C78">
         <v>1051</v>
@@ -8510,7 +8698,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="C79">
         <v>738</v>
@@ -8596,7 +8784,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="C80">
         <v>1090</v>
@@ -8682,7 +8870,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="C81">
         <v>659</v>
@@ -8768,7 +8956,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="C82">
         <v>841</v>
@@ -8854,7 +9042,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C83">
         <v>648</v>
@@ -8940,7 +9128,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="C84">
         <v>684</v>
@@ -9026,7 +9214,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C85">
         <v>1016</v>
@@ -9112,7 +9300,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C86">
         <v>1087</v>
@@ -9198,7 +9386,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="C87">
         <v>903</v>
@@ -9284,7 +9472,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="C88">
         <v>1010</v>
@@ -9370,7 +9558,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="C89">
         <v>1088</v>
@@ -9456,7 +9644,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="C90">
         <v>953</v>
@@ -9542,7 +9730,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="C91">
         <v>1110</v>
@@ -9628,7 +9816,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="C92">
         <v>1013</v>
@@ -9714,7 +9902,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="C93">
         <v>660</v>
@@ -9800,7 +9988,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="C94">
         <v>713</v>
@@ -9886,7 +10074,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="C95">
         <v>604</v>
@@ -9972,7 +10160,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="C96">
         <v>886</v>
@@ -10058,7 +10246,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="C97">
         <v>847</v>
@@ -10144,7 +10332,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="C98">
         <v>1100</v>
@@ -10230,7 +10418,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="C99">
         <v>348</v>
@@ -10316,7 +10504,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="C100">
         <v>658</v>
@@ -10402,7 +10590,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="C101">
         <v>654</v>
@@ -10488,7 +10676,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="C102">
         <v>589</v>
@@ -10574,7 +10762,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="C103">
         <v>1089</v>
@@ -10660,7 +10848,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="C104">
         <v>683</v>
@@ -10746,7 +10934,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="C105">
         <v>585</v>
@@ -10832,7 +11020,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="C106">
         <v>726</v>
@@ -10918,7 +11106,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="C107">
         <v>863</v>
@@ -11004,7 +11192,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="C108">
         <v>1040</v>
@@ -11090,7 +11278,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="C109">
         <v>997</v>
@@ -11176,7 +11364,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="C110">
         <v>1070</v>
@@ -11262,7 +11450,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="C111">
         <v>1065</v>
@@ -11348,7 +11536,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="C112">
         <v>862</v>
@@ -11434,7 +11622,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="C113">
         <v>1077</v>
@@ -11520,7 +11708,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="C114">
         <v>1155</v>
@@ -11606,7 +11794,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="C115">
         <v>1189</v>
@@ -11692,7 +11880,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="C116">
         <v>726</v>
@@ -11778,7 +11966,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="C117">
         <v>483</v>
@@ -11864,7 +12052,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="C118">
         <v>1079</v>
@@ -11950,7 +12138,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="C119">
         <v>692</v>
@@ -12036,7 +12224,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="C120">
         <v>877</v>
@@ -12122,7 +12310,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="C121">
         <v>721</v>
@@ -12208,7 +12396,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="C122">
         <v>582</v>
@@ -12294,7 +12482,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="C123">
         <v>1136</v>
@@ -12380,7 +12568,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="C124">
         <v>1048</v>
@@ -12466,7 +12654,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="C125">
         <v>561</v>
@@ -12552,7 +12740,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="C126">
         <v>1132</v>
@@ -12638,7 +12826,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="C127">
         <v>1175</v>
@@ -12724,7 +12912,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="C128">
         <v>593</v>
@@ -12810,7 +12998,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="C129">
         <v>789</v>
@@ -12896,7 +13084,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="C130">
         <v>1197</v>
@@ -12982,7 +13170,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="C131">
         <v>883</v>
@@ -13068,7 +13256,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="C132">
         <v>686</v>
@@ -13154,7 +13342,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="C133">
         <v>633</v>
@@ -13240,7 +13428,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="C134">
         <v>1070</v>
@@ -13326,7 +13514,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="C135">
         <v>868</v>
@@ -13412,7 +13600,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="C136">
         <v>987</v>
@@ -13498,7 +13686,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="C137">
         <v>716</v>
@@ -13584,7 +13772,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="C138">
         <v>1039</v>
@@ -13670,7 +13858,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="C139">
         <v>870</v>
@@ -13756,7 +13944,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="C140">
         <v>649</v>
@@ -13842,7 +14030,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="C141">
         <v>726</v>
@@ -13928,7 +14116,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="C142">
         <v>715</v>
@@ -14014,7 +14202,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="C143">
         <v>700</v>
@@ -14100,7 +14288,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="C144">
         <v>889</v>
@@ -14186,7 +14374,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="C145">
         <v>382</v>
@@ -14272,7 +14460,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="C146">
         <v>1039</v>
@@ -14358,7 +14546,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="C147">
         <v>1057</v>
@@ -14444,7 +14632,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="C148">
         <v>975</v>
@@ -14530,7 +14718,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="C149">
         <v>621</v>
@@ -14616,7 +14804,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="C150">
         <v>763</v>
@@ -14702,7 +14890,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="C151">
         <v>664</v>
@@ -14788,7 +14976,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="C152">
         <v>801</v>
@@ -14874,7 +15062,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="C153">
         <v>856</v>
@@ -14960,7 +15148,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="C154">
         <v>653</v>
@@ -15046,7 +15234,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="C155">
         <v>582</v>
@@ -15132,7 +15320,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="C156">
         <v>866</v>
@@ -15218,7 +15406,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="C157">
         <v>843</v>
@@ -15304,7 +15492,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="C158">
         <v>660</v>
@@ -15390,7 +15578,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="C159">
         <v>770</v>
@@ -15476,7 +15664,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="C160">
         <v>689</v>
@@ -15562,7 +15750,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="C161">
         <v>661</v>
@@ -15648,7 +15836,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="C162">
         <v>1017</v>
@@ -15734,7 +15922,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="C163">
         <v>833</v>
@@ -15820,7 +16008,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="C164">
         <v>885</v>
@@ -15906,7 +16094,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="C165">
         <v>802</v>
@@ -15992,7 +16180,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="C166">
         <v>732</v>
@@ -16078,7 +16266,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="C167">
         <v>940</v>
@@ -16164,7 +16352,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="C168">
         <v>996</v>
@@ -16250,7 +16438,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="C169">
         <v>803</v>
@@ -16336,7 +16524,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="C170">
         <v>687</v>
@@ -16422,7 +16610,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="C171">
         <v>1033</v>
@@ -16508,7 +16696,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C172">
         <v>509</v>
@@ -16594,7 +16782,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="C173">
         <v>529</v>
@@ -16680,7 +16868,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="C174">
         <v>474</v>
@@ -16766,7 +16954,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="C175">
         <v>812</v>
@@ -16852,7 +17040,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="C176">
         <v>981</v>
@@ -16938,7 +17126,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="C177">
         <v>792</v>
@@ -17024,7 +17212,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="C178">
         <v>620</v>
@@ -17110,7 +17298,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="C179">
         <v>760</v>
@@ -17196,7 +17384,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="C180">
         <v>828</v>
@@ -17282,7 +17470,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="C181">
         <v>911</v>
@@ -17368,7 +17556,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="C182">
         <v>683</v>
@@ -17454,7 +17642,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="C183">
         <v>589</v>
@@ -17540,7 +17728,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="C184">
         <v>491</v>
@@ -17626,7 +17814,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="C185">
         <v>575</v>
@@ -17712,7 +17900,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="C186">
         <v>634</v>
@@ -17798,7 +17986,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C187">
         <v>632</v>
@@ -17884,7 +18072,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C188">
         <v>1042</v>
@@ -17970,7 +18158,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="C189">
         <v>308</v>
@@ -18056,7 +18244,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="C190">
         <v>731</v>
@@ -18142,7 +18330,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="C191">
         <v>1195</v>
@@ -18228,7 +18416,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="C192">
         <v>1200</v>
@@ -18314,7 +18502,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="C193">
         <v>862</v>
@@ -18400,7 +18588,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="C194">
         <v>743</v>
@@ -18486,7 +18674,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="C195">
         <v>609</v>
@@ -18572,7 +18760,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="C196">
         <v>745</v>
@@ -18658,7 +18846,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C197">
         <v>589</v>
@@ -18744,7 +18932,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="C198">
         <v>1022</v>
@@ -18830,7 +19018,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="C199">
         <v>1021</v>
@@ -18916,7 +19104,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="C200">
         <v>1017</v>
@@ -19002,7 +19190,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="C201">
         <v>766</v>
@@ -19088,7 +19276,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="C202">
         <v>1154</v>
@@ -19174,7 +19362,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="C203">
         <v>607</v>
@@ -19260,7 +19448,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="C204">
         <v>688</v>
@@ -19346,7 +19534,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>205</v>
+        <v>232</v>
       </c>
       <c r="C205">
         <v>883</v>
@@ -19432,7 +19620,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="C206">
         <v>1174</v>
@@ -19518,7 +19706,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="C207">
         <v>943</v>
@@ -19604,7 +19792,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="C208">
         <v>986</v>
@@ -19690,7 +19878,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="C209">
         <v>929</v>
@@ -19776,7 +19964,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="C210">
         <v>980</v>
@@ -19862,7 +20050,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="C211">
         <v>616</v>
@@ -19948,7 +20136,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="C212">
         <v>667</v>
@@ -20034,7 +20222,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C213">
         <v>454</v>
@@ -20120,7 +20308,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="C214">
         <v>1083</v>
@@ -20206,7 +20394,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="C215">
         <v>1145</v>
@@ -20292,7 +20480,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="C216">
         <v>403</v>
@@ -20378,7 +20566,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="C217">
         <v>709</v>
@@ -20464,7 +20652,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="C218">
         <v>895</v>
@@ -20550,7 +20738,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="C219">
         <v>1125</v>
@@ -20636,7 +20824,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="C220">
         <v>864</v>
@@ -20722,7 +20910,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="C221">
         <v>1020</v>
@@ -20808,7 +20996,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="C222">
         <v>609</v>
@@ -20894,7 +21082,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="C223">
         <v>1072</v>
@@ -20980,7 +21168,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="C224">
         <v>931</v>
@@ -21066,7 +21254,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>225</v>
+        <v>252</v>
       </c>
       <c r="C225">
         <v>770</v>
@@ -21152,7 +21340,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="C226">
         <v>618</v>
@@ -21238,7 +21426,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="C227">
         <v>992</v>
@@ -21324,7 +21512,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="C228">
         <v>396</v>
@@ -21410,7 +21598,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="C229">
         <v>912</v>
@@ -21496,7 +21684,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="C230">
         <v>715</v>
@@ -21582,7 +21770,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="C231">
         <v>702</v>
@@ -21668,7 +21856,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="C232">
         <v>734</v>
@@ -21754,7 +21942,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="C233">
         <v>604</v>
@@ -21840,7 +22028,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="C234">
         <v>1165</v>
@@ -21926,7 +22114,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="C235">
         <v>405</v>
@@ -22012,7 +22200,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="C236">
         <v>719</v>
@@ -22098,7 +22286,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="C237">
         <v>675</v>
@@ -22184,7 +22372,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>238</v>
+        <v>265</v>
       </c>
       <c r="C238">
         <v>1057</v>
@@ -22270,7 +22458,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="C239">
         <v>522</v>
@@ -22356,7 +22544,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="C240">
         <v>455</v>
@@ -22442,7 +22630,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="C241">
         <v>752</v>
@@ -22528,7 +22716,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="C242">
         <v>728</v>
@@ -22614,7 +22802,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="C243">
         <v>443</v>
@@ -22700,7 +22888,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
+        <v>271</v>
       </c>
       <c r="C244">
         <v>885</v>
@@ -22786,7 +22974,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="C245">
         <v>758</v>
@@ -22872,7 +23060,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>246</v>
+        <v>273</v>
       </c>
       <c r="C246">
         <v>624</v>
@@ -22958,7 +23146,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="C247">
         <v>1119</v>
@@ -23044,7 +23232,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="C248">
         <v>962</v>
@@ -23130,7 +23318,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="C249">
         <v>1012</v>
@@ -23216,7 +23404,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="C250">
         <v>865</v>
@@ -23302,7 +23490,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="C251">
         <v>509</v>
@@ -23388,7 +23576,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="C252">
         <v>910</v>
@@ -23474,7 +23662,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="C253">
         <v>659</v>
@@ -23560,7 +23748,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="C254">
         <v>478</v>
@@ -23646,7 +23834,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="C255">
         <v>999</v>
@@ -23732,7 +23920,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="C256">
         <v>568</v>
@@ -23818,7 +24006,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="C257">
         <v>699</v>
@@ -23904,7 +24092,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="C258">
         <v>789</v>
@@ -23990,7 +24178,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="C259">
         <v>1198</v>
@@ -24076,7 +24264,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="C260">
         <v>764</v>
@@ -24162,7 +24350,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="C261">
         <v>737</v>
@@ -24248,7 +24436,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="C262">
         <v>437</v>
@@ -24334,7 +24522,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="C263">
         <v>772</v>
@@ -24420,7 +24608,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="C264">
         <v>470</v>
@@ -24506,7 +24694,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="C265">
         <v>564</v>
@@ -24592,7 +24780,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="C266">
         <v>854</v>
@@ -24678,7 +24866,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="C267">
         <v>933</v>
@@ -24764,7 +24952,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="C268">
         <v>846</v>
@@ -24850,7 +25038,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="C269">
         <v>436</v>
@@ -24936,7 +25124,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="C270">
         <v>217</v>
@@ -25022,7 +25210,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="C271">
         <v>720</v>
@@ -25108,7 +25296,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="C272">
         <v>742</v>
@@ -25194,7 +25382,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="C273">
         <v>905</v>
@@ -25280,7 +25468,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="C274">
         <v>1027</v>
@@ -25366,7 +25554,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="C275">
         <v>598</v>
@@ -25452,7 +25640,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="C276">
         <v>488</v>
@@ -25538,7 +25726,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="C277">
         <v>1105</v>
@@ -25624,7 +25812,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="C278">
         <v>976</v>
@@ -25710,7 +25898,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="C279">
         <v>759</v>
@@ -25796,7 +25984,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>280</v>
+        <v>307</v>
       </c>
       <c r="C280">
         <v>764</v>
@@ -25882,7 +26070,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="C281">
         <v>1059</v>
@@ -25968,7 +26156,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="C282">
         <v>866</v>
@@ -26054,7 +26242,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="C283">
         <v>778</v>
@@ -26140,7 +26328,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>284</v>
+        <v>311</v>
       </c>
       <c r="C284">
         <v>656</v>
@@ -26226,7 +26414,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>285</v>
+        <v>312</v>
       </c>
       <c r="C285">
         <v>770</v>
@@ -26312,7 +26500,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="C286">
         <v>717</v>
@@ -26398,7 +26586,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="C287">
         <v>550</v>
@@ -26484,7 +26672,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="C288">
         <v>949</v>
@@ -26570,7 +26758,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>289</v>
+        <v>316</v>
       </c>
       <c r="C289">
         <v>1139</v>
@@ -26656,7 +26844,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="C290">
         <v>623</v>
@@ -26742,7 +26930,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="C291">
         <v>1106</v>
@@ -26828,7 +27016,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>292</v>
+        <v>319</v>
       </c>
       <c r="C292">
         <v>905</v>
@@ -26914,7 +27102,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>293</v>
+        <v>320</v>
       </c>
       <c r="C293">
         <v>853</v>
@@ -27000,7 +27188,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="C294">
         <v>774</v>
@@ -27086,7 +27274,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="C295">
         <v>1064</v>
@@ -27172,7 +27360,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="C296">
         <v>1170</v>
@@ -27258,7 +27446,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="C297">
         <v>855</v>
@@ -27344,7 +27532,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>298</v>
+        <v>325</v>
       </c>
       <c r="C298">
         <v>432</v>
@@ -27430,7 +27618,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="C299">
         <v>519</v>
@@ -27516,7 +27704,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>299</v>
+        <v>326</v>
       </c>
       <c r="C300">
         <v>757</v>
@@ -27602,7 +27790,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="C301">
         <v>785</v>
@@ -27688,7 +27876,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="C302">
         <v>1096</v>
@@ -27774,7 +27962,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>302</v>
+        <v>329</v>
       </c>
       <c r="C303">
         <v>1120</v>
@@ -27860,7 +28048,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="C304">
         <v>725</v>
@@ -27946,7 +28134,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>304</v>
+        <v>331</v>
       </c>
       <c r="C305">
         <v>765</v>
@@ -28032,7 +28220,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>305</v>
+        <v>332</v>
       </c>
       <c r="C306">
         <v>1193</v>
@@ -28118,7 +28306,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>306</v>
+        <v>333</v>
       </c>
       <c r="C307">
         <v>1146</v>
@@ -28204,7 +28392,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>307</v>
+        <v>334</v>
       </c>
       <c r="C308">
         <v>831</v>
@@ -28290,7 +28478,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>308</v>
+        <v>335</v>
       </c>
       <c r="C309">
         <v>809</v>
@@ -28376,7 +28564,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>309</v>
+        <v>336</v>
       </c>
       <c r="C310">
         <v>920</v>
@@ -28462,7 +28650,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>310</v>
+        <v>337</v>
       </c>
       <c r="C311">
         <v>966</v>
@@ -28548,7 +28736,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="C312">
         <v>696</v>
@@ -28634,7 +28822,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>312</v>
+        <v>339</v>
       </c>
       <c r="C313">
         <v>1199</v>
@@ -28720,7 +28908,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>313</v>
+        <v>340</v>
       </c>
       <c r="C314">
         <v>1190</v>
@@ -28806,7 +28994,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="C315">
         <v>707</v>
@@ -28892,7 +29080,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>315</v>
+        <v>342</v>
       </c>
       <c r="C316">
         <v>676</v>
@@ -28978,7 +29166,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>316</v>
+        <v>343</v>
       </c>
       <c r="C317">
         <v>1150</v>
@@ -29064,7 +29252,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>317</v>
+        <v>344</v>
       </c>
       <c r="C318">
         <v>1118</v>
@@ -29150,7 +29338,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>318</v>
+        <v>345</v>
       </c>
       <c r="C319">
         <v>846</v>
@@ -29236,7 +29424,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>319</v>
+        <v>346</v>
       </c>
       <c r="C320">
         <v>888</v>
@@ -29322,7 +29510,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="C321">
         <v>675</v>
@@ -29408,7 +29596,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="C322">
         <v>890</v>
@@ -29494,7 +29682,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="C323">
         <v>793</v>
@@ -29580,7 +29768,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="C324">
         <v>860</v>
@@ -29666,7 +29854,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="C325">
         <v>784</v>
@@ -29752,7 +29940,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="C326">
         <v>779</v>
@@ -29838,7 +30026,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="C327">
         <v>712</v>
@@ -29924,7 +30112,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="C328">
         <v>1183</v>
@@ -30010,7 +30198,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="C329">
         <v>728</v>
@@ -30096,7 +30284,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="C330">
         <v>717</v>
@@ -30182,7 +30370,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="C331">
         <v>585</v>
@@ -30268,7 +30456,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="C332">
         <v>890</v>
@@ -30354,7 +30542,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>332</v>
+        <v>359</v>
       </c>
       <c r="C333">
         <v>750</v>
@@ -30440,7 +30628,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>333</v>
+        <v>360</v>
       </c>
       <c r="C334">
         <v>910</v>
@@ -30526,7 +30714,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>334</v>
+        <v>361</v>
       </c>
       <c r="C335">
         <v>791</v>
@@ -30612,7 +30800,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="C336">
         <v>1019</v>
@@ -30698,7 +30886,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="C337">
         <v>306</v>
@@ -30784,7 +30972,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>337</v>
+        <v>364</v>
       </c>
       <c r="C338">
         <v>714</v>
@@ -30870,7 +31058,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>338</v>
+        <v>365</v>
       </c>
       <c r="C339">
         <v>1197</v>
@@ -30956,7 +31144,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>339</v>
+        <v>366</v>
       </c>
       <c r="C340">
         <v>491</v>
@@ -31042,7 +31230,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>340</v>
+        <v>367</v>
       </c>
       <c r="C341">
         <v>1059</v>
@@ -31128,7 +31316,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>341</v>
+        <v>368</v>
       </c>
       <c r="C342">
         <v>916</v>
@@ -31214,7 +31402,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>342</v>
+        <v>369</v>
       </c>
       <c r="C343">
         <v>513</v>
@@ -31300,7 +31488,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="C344">
         <v>1081</v>
@@ -31386,7 +31574,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>344</v>
+        <v>371</v>
       </c>
       <c r="C345">
         <v>790</v>
@@ -31472,7 +31660,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>345</v>
+        <v>372</v>
       </c>
       <c r="C346">
         <v>710</v>
@@ -31558,7 +31746,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="C347">
         <v>698</v>
@@ -31644,7 +31832,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>347</v>
+        <v>374</v>
       </c>
       <c r="C348">
         <v>975</v>
@@ -31730,7 +31918,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="C349">
         <v>759</v>
@@ -31816,7 +32004,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>349</v>
+        <v>376</v>
       </c>
       <c r="C350">
         <v>689</v>
@@ -31902,7 +32090,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>350</v>
+        <v>377</v>
       </c>
       <c r="C351">
         <v>928</v>
@@ -31988,7 +32176,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>351</v>
+        <v>378</v>
       </c>
       <c r="C352">
         <v>432</v>
@@ -32074,7 +32262,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="C353">
         <v>869</v>
@@ -32160,7 +32348,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>353</v>
+        <v>380</v>
       </c>
       <c r="C354">
         <v>1046</v>
@@ -32246,7 +32434,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="C355">
         <v>1163</v>
@@ -32332,7 +32520,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="C356">
         <v>1093</v>
@@ -32418,7 +32606,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="C357">
         <v>985</v>
@@ -32504,7 +32692,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="C358">
         <v>884</v>
@@ -32590,7 +32778,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="C359">
         <v>851</v>
@@ -32676,7 +32864,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="C360">
         <v>816</v>
@@ -32762,7 +32950,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>360</v>
+        <v>387</v>
       </c>
       <c r="C361">
         <v>820</v>
@@ -32848,7 +33036,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="C362">
         <v>688</v>
@@ -32934,7 +33122,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="C363">
         <v>709</v>
@@ -33020,7 +33208,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>363</v>
+        <v>390</v>
       </c>
       <c r="C364">
         <v>603</v>
@@ -33106,7 +33294,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="C365">
         <v>719</v>
@@ -33192,7 +33380,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="C366">
         <v>515</v>
@@ -33278,7 +33466,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>366</v>
+        <v>393</v>
       </c>
       <c r="C367">
         <v>1180</v>
@@ -33364,7 +33552,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>367</v>
+        <v>394</v>
       </c>
       <c r="C368">
         <v>1142</v>
@@ -33450,7 +33638,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="C369">
         <v>827</v>
@@ -33536,7 +33724,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="C370">
         <v>823</v>
@@ -33622,7 +33810,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="C371">
         <v>1111</v>
@@ -33708,7 +33896,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="C372">
         <v>985</v>
@@ -33794,7 +33982,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="C373">
         <v>901</v>
@@ -33880,7 +34068,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="C374">
         <v>1138</v>
@@ -33966,7 +34154,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="C375">
         <v>701</v>
@@ -34052,7 +34240,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="C376">
         <v>758</v>
@@ -34138,7 +34326,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="C377">
         <v>742</v>
@@ -34224,7 +34412,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="C378">
         <v>1059</v>
@@ -34310,7 +34498,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>378</v>
+        <v>405</v>
       </c>
       <c r="C379">
         <v>649</v>
@@ -34396,7 +34584,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>379</v>
+        <v>406</v>
       </c>
       <c r="C380">
         <v>574</v>
@@ -34482,7 +34670,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>380</v>
+        <v>407</v>
       </c>
       <c r="C381">
         <v>1112</v>
@@ -34568,7 +34756,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="C382">
         <v>868</v>
@@ -34654,7 +34842,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="C383">
         <v>999</v>
@@ -34740,7 +34928,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>383</v>
+        <v>410</v>
       </c>
       <c r="C384">
         <v>1012</v>
@@ -34826,7 +35014,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="C385">
         <v>1166</v>
@@ -34912,7 +35100,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="C386">
         <v>798</v>
@@ -34998,7 +35186,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="C387">
         <v>786</v>
@@ -35084,7 +35272,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>387</v>
+        <v>414</v>
       </c>
       <c r="C388">
         <v>1113</v>
@@ -35170,7 +35358,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="C389">
         <v>901</v>
@@ -35256,7 +35444,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="C390">
         <v>798</v>
@@ -35342,7 +35530,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>390</v>
+        <v>417</v>
       </c>
       <c r="C391">
         <v>779</v>
@@ -35428,7 +35616,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="C392">
         <v>862</v>
@@ -35514,7 +35702,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>392</v>
+        <v>419</v>
       </c>
       <c r="C393">
         <v>1174</v>
@@ -35600,7 +35788,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="C394">
         <v>1100</v>
@@ -35686,7 +35874,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="C395">
         <v>698</v>
@@ -35772,7 +35960,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>395</v>
+        <v>422</v>
       </c>
       <c r="C396">
         <v>641</v>
@@ -35858,7 +36046,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="C397">
         <v>1020</v>
@@ -35944,7 +36132,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="C398">
         <v>737</v>
@@ -36030,7 +36218,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="C399">
         <v>1119</v>
@@ -36116,7 +36304,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>399</v>
+        <v>426</v>
       </c>
       <c r="C400">
         <v>1099</v>
@@ -36202,7 +36390,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>400</v>
+        <v>427</v>
       </c>
       <c r="C401">
         <v>1174</v>
@@ -36288,7 +36476,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>401</v>
+        <v>428</v>
       </c>
       <c r="C402">
         <v>993</v>
@@ -36374,7 +36562,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>402</v>
+        <v>429</v>
       </c>
       <c r="C403">
         <v>1142</v>
@@ -36460,7 +36648,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>403</v>
+        <v>430</v>
       </c>
       <c r="C404">
         <v>851</v>
@@ -36546,7 +36734,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>404</v>
+        <v>431</v>
       </c>
       <c r="C405">
         <v>1164</v>
@@ -36632,7 +36820,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>405</v>
+        <v>432</v>
       </c>
       <c r="C406">
         <v>1187</v>
@@ -36718,7 +36906,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>406</v>
+        <v>433</v>
       </c>
       <c r="C407">
         <v>953</v>
@@ -36804,7 +36992,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>407</v>
+        <v>434</v>
       </c>
       <c r="C408">
         <v>608</v>
@@ -36890,7 +37078,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="C409">
         <v>729</v>
@@ -36976,7 +37164,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="C410">
         <v>701</v>
@@ -37062,7 +37250,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="C411">
         <v>811</v>
@@ -37148,7 +37336,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>411</v>
+        <v>438</v>
       </c>
       <c r="C412">
         <v>1161</v>
@@ -37234,7 +37422,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>412</v>
+        <v>439</v>
       </c>
       <c r="C413">
         <v>890</v>
@@ -37320,7 +37508,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>413</v>
+        <v>440</v>
       </c>
       <c r="C414">
         <v>702</v>
@@ -37406,7 +37594,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="C415">
         <v>1153</v>
@@ -37492,7 +37680,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>415</v>
+        <v>442</v>
       </c>
       <c r="C416">
         <v>1194</v>
@@ -37578,7 +37766,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>416</v>
+        <v>443</v>
       </c>
       <c r="C417">
         <v>724</v>
@@ -37664,7 +37852,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="C418">
         <v>654</v>
@@ -37750,7 +37938,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>418</v>
+        <v>445</v>
       </c>
       <c r="C419">
         <v>903</v>
@@ -37836,7 +38024,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>419</v>
+        <v>446</v>
       </c>
       <c r="C420">
         <v>1102</v>
@@ -37922,7 +38110,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="C421">
         <v>961</v>
@@ -38008,7 +38196,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>421</v>
+        <v>448</v>
       </c>
       <c r="C422">
         <v>941</v>
@@ -38094,7 +38282,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>422</v>
+        <v>449</v>
       </c>
       <c r="C423">
         <v>944</v>
@@ -38180,7 +38368,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="C424">
         <v>430</v>
@@ -38266,7 +38454,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="C425">
         <v>930</v>
@@ -38352,7 +38540,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>425</v>
+        <v>452</v>
       </c>
       <c r="C426">
         <v>834</v>
@@ -38438,7 +38626,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="C427">
         <v>972</v>
@@ -38524,7 +38712,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>427</v>
+        <v>454</v>
       </c>
       <c r="C428">
         <v>1073</v>
@@ -38610,7 +38798,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>428</v>
+        <v>455</v>
       </c>
       <c r="C429">
         <v>774</v>
@@ -38696,7 +38884,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>429</v>
+        <v>456</v>
       </c>
       <c r="C430">
         <v>551</v>
@@ -38782,7 +38970,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>430</v>
+        <v>457</v>
       </c>
       <c r="C431">
         <v>674</v>
@@ -38868,7 +39056,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>431</v>
+        <v>458</v>
       </c>
       <c r="C432">
         <v>367</v>
@@ -38954,7 +39142,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>432</v>
+        <v>459</v>
       </c>
       <c r="C433">
         <v>947</v>
@@ -39040,7 +39228,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>433</v>
+        <v>460</v>
       </c>
       <c r="C434">
         <v>1068</v>
@@ -39126,7 +39314,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>434</v>
+        <v>461</v>
       </c>
       <c r="C435">
         <v>568</v>
@@ -39212,7 +39400,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>435</v>
+        <v>462</v>
       </c>
       <c r="C436">
         <v>1063</v>
@@ -39298,7 +39486,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>436</v>
+        <v>463</v>
       </c>
       <c r="C437">
         <v>932</v>
@@ -39384,7 +39572,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="C438">
         <v>888</v>
@@ -39470,7 +39658,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>438</v>
+        <v>465</v>
       </c>
       <c r="C439">
         <v>1189</v>
@@ -39556,7 +39744,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>439</v>
+        <v>466</v>
       </c>
       <c r="C440">
         <v>1029</v>
@@ -39642,7 +39830,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>440</v>
+        <v>467</v>
       </c>
       <c r="C441">
         <v>988</v>
@@ -39728,7 +39916,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>441</v>
+        <v>468</v>
       </c>
       <c r="C442">
         <v>1017</v>
@@ -39814,7 +40002,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>442</v>
+        <v>469</v>
       </c>
       <c r="C443">
         <v>537</v>
@@ -39900,7 +40088,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>443</v>
+        <v>470</v>
       </c>
       <c r="C444">
         <v>1071</v>
@@ -39986,7 +40174,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>444</v>
+        <v>471</v>
       </c>
       <c r="C445">
         <v>1127</v>
@@ -40072,7 +40260,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="C446">
         <v>1199</v>
@@ -40158,7 +40346,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="C447">
         <v>658</v>
@@ -40244,7 +40432,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="C448">
         <v>1183</v>
@@ -40330,7 +40518,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>448</v>
+        <v>475</v>
       </c>
       <c r="C449">
         <v>997</v>
@@ -40416,7 +40604,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>449</v>
+        <v>476</v>
       </c>
       <c r="C450">
         <v>1091</v>
@@ -40502,7 +40690,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>450</v>
+        <v>477</v>
       </c>
       <c r="C451">
         <v>1096</v>
@@ -40588,7 +40776,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>451</v>
+        <v>478</v>
       </c>
       <c r="C452">
         <v>670</v>
@@ -40674,7 +40862,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>452</v>
+        <v>479</v>
       </c>
       <c r="C453">
         <v>761</v>
@@ -40760,7 +40948,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>453</v>
+        <v>480</v>
       </c>
       <c r="C454">
         <v>938</v>
@@ -40846,7 +41034,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>454</v>
+        <v>481</v>
       </c>
       <c r="C455">
         <v>832</v>
@@ -40932,7 +41120,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="C456">
         <v>887</v>
@@ -41018,7 +41206,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>456</v>
+        <v>483</v>
       </c>
       <c r="C457">
         <v>414</v>
@@ -41104,7 +41292,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>457</v>
+        <v>484</v>
       </c>
       <c r="C458">
         <v>735</v>
@@ -41190,7 +41378,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>458</v>
+        <v>485</v>
       </c>
       <c r="C459">
         <v>433</v>
@@ -41276,7 +41464,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="s">
-        <v>459</v>
+        <v>486</v>
       </c>
       <c r="C460">
         <v>641</v>
@@ -41362,7 +41550,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="C461">
         <v>517</v>
@@ -41448,7 +41636,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>460</v>
+        <v>487</v>
       </c>
       <c r="C462">
         <v>813</v>
@@ -41534,7 +41722,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="s">
-        <v>461</v>
+        <v>488</v>
       </c>
       <c r="C463">
         <v>541</v>
@@ -41620,7 +41808,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
       <c r="C464">
         <v>691</v>
@@ -41706,7 +41894,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="s">
-        <v>463</v>
+        <v>490</v>
       </c>
       <c r="C465">
         <v>824</v>
@@ -41792,7 +41980,7 @@
         <v>464</v>
       </c>
       <c r="B466" t="s">
-        <v>464</v>
+        <v>491</v>
       </c>
       <c r="C466">
         <v>468</v>
@@ -41878,7 +42066,7 @@
         <v>465</v>
       </c>
       <c r="B467" t="s">
-        <v>465</v>
+        <v>492</v>
       </c>
       <c r="C467">
         <v>1004</v>
@@ -41964,7 +42152,7 @@
         <v>466</v>
       </c>
       <c r="B468" t="s">
-        <v>466</v>
+        <v>493</v>
       </c>
       <c r="C468">
         <v>1061</v>
@@ -42050,7 +42238,7 @@
         <v>467</v>
       </c>
       <c r="B469" t="s">
-        <v>467</v>
+        <v>494</v>
       </c>
       <c r="C469">
         <v>1157</v>
@@ -42136,7 +42324,7 @@
         <v>468</v>
       </c>
       <c r="B470" t="s">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="C470">
         <v>673</v>
@@ -42222,7 +42410,7 @@
         <v>469</v>
       </c>
       <c r="B471" t="s">
-        <v>469</v>
+        <v>496</v>
       </c>
       <c r="C471">
         <v>923</v>
@@ -42308,7 +42496,7 @@
         <v>470</v>
       </c>
       <c r="B472" t="s">
-        <v>470</v>
+        <v>497</v>
       </c>
       <c r="C472">
         <v>838</v>
@@ -42394,7 +42582,7 @@
         <v>471</v>
       </c>
       <c r="B473" t="s">
-        <v>471</v>
+        <v>498</v>
       </c>
       <c r="C473">
         <v>1178</v>
@@ -42480,7 +42668,7 @@
         <v>472</v>
       </c>
       <c r="B474" t="s">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="C474">
         <v>651</v>
@@ -42566,7 +42754,7 @@
         <v>473</v>
       </c>
       <c r="B475" t="s">
-        <v>473</v>
+        <v>500</v>
       </c>
       <c r="C475">
         <v>627</v>
@@ -42652,7 +42840,7 @@
         <v>474</v>
       </c>
       <c r="B476" t="s">
-        <v>474</v>
+        <v>501</v>
       </c>
       <c r="C476">
         <v>1189</v>
@@ -42738,7 +42926,7 @@
         <v>475</v>
       </c>
       <c r="B477" t="s">
-        <v>475</v>
+        <v>502</v>
       </c>
       <c r="C477">
         <v>679</v>
@@ -42824,7 +43012,7 @@
         <v>476</v>
       </c>
       <c r="B478" t="s">
-        <v>476</v>
+        <v>503</v>
       </c>
       <c r="C478">
         <v>885</v>
@@ -42910,7 +43098,7 @@
         <v>477</v>
       </c>
       <c r="B479" t="s">
-        <v>477</v>
+        <v>504</v>
       </c>
       <c r="C479">
         <v>1075</v>
@@ -42996,7 +43184,7 @@
         <v>478</v>
       </c>
       <c r="B480" t="s">
-        <v>478</v>
+        <v>505</v>
       </c>
       <c r="C480">
         <v>1009</v>
@@ -43082,7 +43270,7 @@
         <v>479</v>
       </c>
       <c r="B481" t="s">
-        <v>479</v>
+        <v>506</v>
       </c>
       <c r="C481">
         <v>1004</v>
@@ -43168,7 +43356,7 @@
         <v>480</v>
       </c>
       <c r="B482" t="s">
-        <v>480</v>
+        <v>507</v>
       </c>
       <c r="C482">
         <v>1112</v>
@@ -43254,7 +43442,7 @@
         <v>481</v>
       </c>
       <c r="B483" t="s">
-        <v>481</v>
+        <v>508</v>
       </c>
       <c r="C483">
         <v>1151</v>
@@ -43340,7 +43528,7 @@
         <v>482</v>
       </c>
       <c r="B484" t="s">
-        <v>482</v>
+        <v>509</v>
       </c>
       <c r="C484">
         <v>754</v>
@@ -43426,7 +43614,7 @@
         <v>483</v>
       </c>
       <c r="B485" t="s">
-        <v>483</v>
+        <v>510</v>
       </c>
       <c r="C485">
         <v>722</v>
